--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260914.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>191,470,013</t>
+          <t>30,260,628</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>30,260,628</t>
+          <t>191,470,013</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>69,320,442</t>
+          <t>26,200,936</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>26,200,936</t>
+          <t>87,625,862</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>87,625,862</t>
+          <t>69,320,442</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>113,624,512</t>
+          <t>17,499,640</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>17,499,640</t>
+          <t>113,624,512</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>26,226,377</t>
+          <t>247,295,862</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>247,295,862</t>
+          <t>26,226,377</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
